--- a/output/graficos_dimensiones/comunal_d_env_a_2019_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:15</t>
+    <t xml:space="preserve">2026-09-10 01:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:29</t>
+    <t xml:space="preserve">2026-09-12 22:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_la araucania.xlsx
@@ -63,48 +63,48 @@
     <t xml:space="preserve">Victoria</t>
   </si>
   <si>
+    <t xml:space="preserve">Saavedra</t>
+  </si>
+  <si>
     <t xml:space="preserve">Traiguén</t>
   </si>
   <si>
     <t xml:space="preserve">Pitrufquén</t>
   </si>
   <si>
-    <t xml:space="preserve">Saavedra</t>
-  </si>
-  <si>
     <t xml:space="preserve">Loncoche</t>
   </si>
   <si>
     <t xml:space="preserve">Nueva Imperial</t>
   </si>
   <si>
+    <t xml:space="preserve">Lumaco</t>
+  </si>
+  <si>
     <t xml:space="preserve">Purén</t>
   </si>
   <si>
-    <t xml:space="preserve">Lumaco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Carahue</t>
   </si>
   <si>
+    <t xml:space="preserve">Galvarino</t>
+  </si>
+  <si>
     <t xml:space="preserve">Angol</t>
   </si>
   <si>
-    <t xml:space="preserve">Galvarino</t>
-  </si>
-  <si>
     <t xml:space="preserve">Perquenco</t>
   </si>
   <si>
+    <t xml:space="preserve">Lonquimay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temuco</t>
+  </si>
+  <si>
     <t xml:space="preserve">Renaico</t>
   </si>
   <si>
-    <t xml:space="preserve">Lonquimay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Temuco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Collipulli</t>
   </si>
   <si>
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:41</t>
+    <t xml:space="preserve">2026-09-24 00:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -574,7 +574,7 @@
         <v>2019</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>126.66</v>
+        <v>136.63</v>
       </c>
     </row>
     <row r="3">
@@ -591,7 +591,7 @@
         <v>2019</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>121.81</v>
+        <v>130.73</v>
       </c>
     </row>
     <row r="4">
@@ -608,7 +608,7 @@
         <v>2019</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>120.63</v>
+        <v>127.99</v>
       </c>
     </row>
     <row r="5">
@@ -625,7 +625,7 @@
         <v>2019</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>118.27</v>
+        <v>127.88</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         <v>2019</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>118.25</v>
+        <v>127.39</v>
       </c>
     </row>
     <row r="7">
@@ -659,7 +659,7 @@
         <v>2019</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>115.78</v>
+        <v>124.89</v>
       </c>
     </row>
     <row r="8">
@@ -676,7 +676,7 @@
         <v>2019</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>115.3</v>
+        <v>123.94</v>
       </c>
     </row>
     <row r="9">
@@ -693,7 +693,7 @@
         <v>2019</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>110.81</v>
+        <v>118.83</v>
       </c>
     </row>
     <row r="10">
@@ -710,7 +710,7 @@
         <v>2019</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>110.15</v>
+        <v>117.54</v>
       </c>
     </row>
     <row r="11">
@@ -721,13 +721,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>9210</v>
+        <v>9116</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>108.56</v>
+        <v>116.35</v>
       </c>
     </row>
     <row r="12">
@@ -738,13 +738,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>9114</v>
+        <v>9210</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>107.74</v>
+        <v>116.23</v>
       </c>
     </row>
     <row r="13">
@@ -755,13 +755,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>9116</v>
+        <v>9114</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>107.06</v>
+        <v>115.78</v>
       </c>
     </row>
     <row r="14">
@@ -778,7 +778,7 @@
         <v>2019</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>106.39</v>
+        <v>114.78</v>
       </c>
     </row>
     <row r="15">
@@ -795,7 +795,7 @@
         <v>2019</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>105.09</v>
+        <v>113.77</v>
       </c>
     </row>
     <row r="16">
@@ -806,13 +806,13 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>9208</v>
+        <v>9207</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>101.35</v>
+        <v>110.22</v>
       </c>
     </row>
     <row r="17">
@@ -823,13 +823,13 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>9207</v>
+        <v>9208</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>101.12</v>
+        <v>108.8</v>
       </c>
     </row>
     <row r="18">
@@ -846,7 +846,7 @@
         <v>2019</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>100.22</v>
+        <v>107.24</v>
       </c>
     </row>
     <row r="19">
@@ -857,13 +857,13 @@
         <v>23</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>9201</v>
+        <v>9106</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>92.17</v>
+        <v>99.41</v>
       </c>
     </row>
     <row r="20">
@@ -874,13 +874,13 @@
         <v>24</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>9106</v>
+        <v>9201</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>92.09</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="21">
@@ -897,7 +897,7 @@
         <v>2019</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>90.16</v>
+        <v>96.78</v>
       </c>
     </row>
     <row r="22">
@@ -908,13 +908,13 @@
         <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>9209</v>
+        <v>9205</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>87.02</v>
+        <v>93.43</v>
       </c>
     </row>
     <row r="23">
@@ -925,13 +925,13 @@
         <v>27</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>9205</v>
+        <v>9101</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>86.94</v>
+        <v>93.09</v>
       </c>
     </row>
     <row r="24">
@@ -942,13 +942,13 @@
         <v>28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>9101</v>
+        <v>9209</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>86.62</v>
+        <v>92.19</v>
       </c>
     </row>
     <row r="25">
@@ -965,7 +965,7 @@
         <v>2019</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>84.84</v>
+        <v>91.12</v>
       </c>
     </row>
     <row r="26">
@@ -982,7 +982,7 @@
         <v>2019</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>84.12</v>
+        <v>90.45</v>
       </c>
     </row>
     <row r="27">
@@ -999,7 +999,7 @@
         <v>2019</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>82.84</v>
+        <v>88.38</v>
       </c>
     </row>
     <row r="28">
@@ -1016,7 +1016,7 @@
         <v>2019</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>81.18</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="29">
@@ -1033,7 +1033,7 @@
         <v>2019</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>80.3</v>
+        <v>86.01</v>
       </c>
     </row>
     <row r="30">
@@ -1050,7 +1050,7 @@
         <v>2019</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>79.93</v>
+        <v>85.97</v>
       </c>
     </row>
     <row r="31">
@@ -1067,7 +1067,7 @@
         <v>2019</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>76.53</v>
+        <v>81.92</v>
       </c>
     </row>
     <row r="32">
@@ -1084,7 +1084,7 @@
         <v>2019</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>71.77</v>
+        <v>77.1</v>
       </c>
     </row>
     <row r="33">
@@ -1101,7 +1101,7 @@
         <v>2019</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>71.48</v>
+        <v>76.21</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:09</t>
+    <t xml:space="preserve">2026-10-02 16:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:10</t>
+    <t xml:space="preserve">2026-10-05 16:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
